--- a/autocana/templates/tsh.xlsx
+++ b/autocana/templates/tsh.xlsx
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wavreith/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jo.goebel\Desktop\TO PRINT (NEW)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA1A527-E0DE-A948-97CD-19C6115680CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64BA786C-A09B-4665-804D-F8436B980206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="template to use" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="COUNTRY_HOUR_FACTOR">'template to use'!$D$66</definedName>
+    <definedName name="COUNTRY_HOUR_FACTOR">'template to use'!$D$71</definedName>
     <definedName name="DAY_OF_WEEK">'template to use'!A$43</definedName>
     <definedName name="MONTHS">'template to use'!$B$42:$B$53</definedName>
     <definedName name="SELECTED_MONTH">'template to use'!$C$42</definedName>
     <definedName name="SELECTED_YEAR">'template to use'!$E$42</definedName>
     <definedName name="YEARS">'template to use'!$D$42:$D$53</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -51,15 +51,23 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Project:
-P9999 = project number (Mandatory!! / ask to your project Manager)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">P9999 = project number (Mandatory!! / ask to your project Manager)
 CPT = Not working for Arhs
 </t>
         </r>
@@ -71,7 +79,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -201,15 +209,23 @@
       <text>
         <r>
           <rPr>
-            <b/>
-            <sz val="8"/>
-            <color rgb="FF000000"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-            <charset val="1"/>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">Project:
-P9999 = project number (Mandatory!! / ask to your project Manager)
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="8"/>
+            <color rgb="FF000000"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">P9999 = project number (Mandatory!! / ask to your project Manager)
 CPT = Not working for Arhs
 </t>
         </r>
@@ -221,7 +237,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -371,7 +387,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -503,7 +519,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -635,7 +651,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -767,7 +783,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -899,7 +915,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -1031,7 +1047,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -1163,7 +1179,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -1295,7 +1311,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -1427,7 +1443,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -1559,7 +1575,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -1691,7 +1707,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -1823,7 +1839,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -1955,7 +1971,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="Arial"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">PM: </t>
         </r>
@@ -2217,7 +2233,7 @@
     <t>Country (BE/LU)</t>
   </si>
   <si>
-    <t>LU</t>
+    <t>BE</t>
   </si>
   <si>
     <t>Version</t>
@@ -2233,7 +2249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -2291,6 +2307,11 @@
       <name val="Tahoma"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3273,9 +3294,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3313,7 +3334,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3419,7 +3440,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3561,7 +3582,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3572,24 +3593,24 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A3:AMJ76"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <dimension ref="A3:AMJ81"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.1640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.83203125" style="3" customWidth="1"/>
-    <col min="3" max="3" width="9.5" style="3" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.5" style="3" customWidth="1"/>
-    <col min="6" max="6" width="6.5" style="3" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="24.7109375" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="6.42578125" style="3" customWidth="1"/>
     <col min="7" max="7" width="6" style="3" customWidth="1"/>
-    <col min="8" max="8" width="5.33203125" style="3" customWidth="1"/>
-    <col min="9" max="39" width="2.6640625" style="3" customWidth="1"/>
-    <col min="40" max="42" width="9.1640625" style="3"/>
-    <col min="43" max="43" width="25.6640625" style="3" customWidth="1"/>
-    <col min="44" max="1024" width="9.1640625" style="3"/>
+    <col min="8" max="8" width="5.28515625" style="3" customWidth="1"/>
+    <col min="9" max="39" width="2.7109375" style="3" customWidth="1"/>
+    <col min="40" max="42" width="9.140625" style="3"/>
+    <col min="43" max="43" width="25.7109375" style="3" customWidth="1"/>
+    <col min="44" max="1024" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.25">
       <c r="G3" s="71"/>
       <c r="H3" s="71"/>
       <c r="I3" s="71"/>
@@ -3624,7 +3645,7 @@
       <c r="AL3" s="71"/>
       <c r="AM3" s="71"/>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.25">
       <c r="G4" s="72" t="s">
         <v>0</v>
       </c>
@@ -3660,13 +3681,13 @@
       <c r="AG4" s="75"/>
       <c r="AH4" s="75"/>
       <c r="AJ4" s="76">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="AK4" s="76"/>
       <c r="AL4" s="76"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.25">
       <c r="G5" s="66"/>
       <c r="H5" s="66"/>
       <c r="I5" s="66"/>
@@ -3701,7 +3722,7 @@
       <c r="AL5" s="66"/>
       <c r="AM5" s="66"/>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A7" s="67" t="s">
         <v>3</v>
       </c>
@@ -3752,7 +3773,7 @@
       <c r="AL7" s="10"/>
       <c r="AM7" s="11"/>
     </row>
-    <row r="8" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>8</v>
       </c>
@@ -3867,12 +3888,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:39" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A9" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B9" s="20" t="str">
-        <f t="shared" ref="B9:B23" si="0">IF(ISBLANK(A9),"",IF(LEFT(A9,1)="P","",VLOOKUP(A9,$A$55:$D$57,2,FALSE())))</f>
+        <f t="shared" ref="B9:B23" si="0">IF(ISBLANK(A9),"",IF(LEFT(A9,1)="P","",VLOOKUP(A9,$A$60:$D$62,2,FALSE())))</f>
         <v>Contract part-time</v>
       </c>
       <c r="C9" s="21"/>
@@ -3880,7 +3901,7 @@
         <v>14</v>
       </c>
       <c r="E9" s="22" t="str">
-        <f t="shared" ref="E9:E23" si="1">IF(ISBLANK(A9),"",IF(LEFT(A9,1)="P","BI",VLOOKUP(A9,$A$55:$D$57,3,FALSE())))</f>
+        <f t="shared" ref="E9:E23" si="1">IF(ISBLANK(A9),"",IF(LEFT(A9,1)="P","BI",VLOOKUP(A9,$A$60:$D$62,3,FALSE())))</f>
         <v>NB-CPT</v>
       </c>
       <c r="F9" s="22"/>
@@ -3926,12 +3947,9 @@
       <c r="AL9" s="22"/>
       <c r="AM9" s="25"/>
     </row>
-    <row r="10" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:39" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A10" s="19"/>
-      <c r="B10" s="20" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
+      <c r="B10" s="20"/>
       <c r="C10" s="21"/>
       <c r="D10" s="20"/>
       <c r="E10" s="22" t="str">
@@ -3979,7 +3997,7 @@
       <c r="AL10" s="22"/>
       <c r="AM10" s="25"/>
     </row>
-    <row r="11" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:39" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A11" s="19"/>
       <c r="B11" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4032,7 +4050,7 @@
       <c r="AL11" s="22"/>
       <c r="AM11" s="25"/>
     </row>
-    <row r="12" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:39" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A12" s="19"/>
       <c r="B12" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4085,7 +4103,7 @@
       <c r="AL12" s="22"/>
       <c r="AM12" s="25"/>
     </row>
-    <row r="13" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:39" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A13" s="19"/>
       <c r="B13" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4138,7 +4156,7 @@
       <c r="AL13" s="22"/>
       <c r="AM13" s="25"/>
     </row>
-    <row r="14" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:39" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A14" s="19"/>
       <c r="B14" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4191,7 +4209,7 @@
       <c r="AL14" s="22"/>
       <c r="AM14" s="25"/>
     </row>
-    <row r="15" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:39" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A15" s="19"/>
       <c r="B15" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4244,7 +4262,7 @@
       <c r="AL15" s="22"/>
       <c r="AM15" s="25"/>
     </row>
-    <row r="16" spans="1:39" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:39" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A16" s="19"/>
       <c r="B16" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4297,7 +4315,7 @@
       <c r="AL16" s="22"/>
       <c r="AM16" s="25"/>
     </row>
-    <row r="17" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:44" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A17" s="19"/>
       <c r="B17" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4350,7 +4368,7 @@
       <c r="AL17" s="22"/>
       <c r="AM17" s="25"/>
     </row>
-    <row r="18" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:44" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A18" s="19"/>
       <c r="B18" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4403,7 +4421,7 @@
       <c r="AL18" s="22"/>
       <c r="AM18" s="25"/>
     </row>
-    <row r="19" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:44" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A19" s="19"/>
       <c r="B19" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4456,7 +4474,7 @@
       <c r="AL19" s="22"/>
       <c r="AM19" s="25"/>
     </row>
-    <row r="20" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:44" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A20" s="19"/>
       <c r="B20" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4509,7 +4527,7 @@
       <c r="AL20" s="22"/>
       <c r="AM20" s="25"/>
     </row>
-    <row r="21" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:44" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A21" s="19"/>
       <c r="B21" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4562,7 +4580,7 @@
       <c r="AL21" s="22"/>
       <c r="AM21" s="25"/>
     </row>
-    <row r="22" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:44" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A22" s="19"/>
       <c r="B22" s="20" t="str">
         <f t="shared" si="0"/>
@@ -4615,7 +4633,7 @@
       <c r="AL22" s="22"/>
       <c r="AM22" s="25"/>
     </row>
-    <row r="23" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:44" s="2" customFormat="1" ht="14.25" x14ac:dyDescent="0.3">
       <c r="A23" s="27"/>
       <c r="B23" s="28" t="str">
         <f t="shared" si="0"/>
@@ -4668,7 +4686,7 @@
       <c r="AL23" s="22"/>
       <c r="AM23" s="25"/>
     </row>
-    <row r="24" spans="1:44" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:44" s="2" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A24" s="33"/>
       <c r="B24" s="34"/>
       <c r="C24" s="34"/>
@@ -4807,7 +4825,7 @@
       <c r="AQ24" s="38"/>
       <c r="AR24" s="38"/>
     </row>
-    <row r="25" spans="1:44" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:44" s="2" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D25" s="70" t="s">
         <v>16</v>
       </c>
@@ -4856,7 +4874,7 @@
       <c r="AQ25" s="38"/>
       <c r="AR25" s="38"/>
     </row>
-    <row r="26" spans="1:44" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:44" s="2" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D26" s="63" t="s">
         <v>17</v>
       </c>
@@ -4874,7 +4892,7 @@
       <c r="AQ26" s="38"/>
       <c r="AR26" s="38"/>
     </row>
-    <row r="27" spans="1:44" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:44" s="2" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
       <c r="D27" s="64" t="s">
         <v>18</v>
       </c>
@@ -4892,15 +4910,15 @@
       <c r="AQ27" s="38"/>
       <c r="AR27" s="38"/>
     </row>
-    <row r="28" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="H28" s="47">
         <f>SUM(H25:H27)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="48"/>
       <c r="B31" s="49"/>
       <c r="C31" s="49"/>
@@ -4941,7 +4959,7 @@
       <c r="AL31" s="49"/>
       <c r="AM31" s="50"/>
     </row>
-    <row r="32" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="51"/>
       <c r="B32" s="65" t="s">
         <v>19</v>
@@ -4983,27 +5001,27 @@
       <c r="AL32" s="65"/>
       <c r="AM32" s="52"/>
     </row>
-    <row r="33" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4"/>
       <c r="AM33" s="52"/>
     </row>
-    <row r="34" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4"/>
       <c r="AM34" s="52"/>
     </row>
-    <row r="35" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4"/>
       <c r="AM35" s="52"/>
     </row>
-    <row r="36" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4"/>
       <c r="AM36" s="52"/>
     </row>
-    <row r="37" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="AM37" s="52"/>
     </row>
-    <row r="38" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
       <c r="B38" s="53" t="s">
         <v>21</v>
@@ -5049,7 +5067,7 @@
       <c r="AL38" s="55"/>
       <c r="AM38" s="52"/>
     </row>
-    <row r="39" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="56"/>
       <c r="B39" s="57"/>
       <c r="C39" s="57"/>
@@ -5090,13 +5108,13 @@
       <c r="AL39" s="57"/>
       <c r="AM39" s="58"/>
     </row>
-    <row r="40" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="41" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="41" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="AP41" s="38"/>
       <c r="AQ41" s="38"/>
       <c r="AR41" s="38"/>
     </row>
-    <row r="42" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="2" t="s">
         <v>2</v>
       </c>
@@ -5105,11 +5123,11 @@
         <v>1</v>
       </c>
       <c r="D42" s="2">
-        <v>2014</v>
+        <v>2025</v>
       </c>
       <c r="E42" s="2">
         <f>MATCH($AJ$4,YEARS,0)</f>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I42" s="2">
         <v>1</v>
@@ -5208,338 +5226,375 @@
       <c r="AQ42" s="38"/>
       <c r="AR42" s="38"/>
     </row>
-    <row r="43" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="2" t="s">
         <v>24</v>
       </c>
       <c r="D43" s="2">
-        <v>2015</v>
+        <v>2026</v>
       </c>
       <c r="I43" s="2">
         <f t="shared" ref="I43:AG43" si="5">WEEKDAY(DATE($D$42+$E$42-1,$C$42,I$42),2)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J43" s="2">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K43" s="2">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L43" s="2">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M43" s="2">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N43" s="2">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O43" s="2">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P43" s="2">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q43" s="2">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R43" s="2">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="S43" s="2">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T43" s="2">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U43" s="2">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="V43" s="2">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W43" s="2">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="X43" s="2">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y43" s="2">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z43" s="2">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AA43" s="2">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AB43" s="2">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC43" s="2">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD43" s="2">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE43" s="2">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF43" s="2">
         <f t="shared" si="5"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG43" s="2">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AH43" s="2">
         <f t="shared" ref="AH43:AM43" si="6">IF(MONTH(DATE($D$42+$E$42-1,$C$42,AH$42))&lt;&gt;SELECTED_MONTH,8,WEEKDAY(DATE($D$42+$E$42-1,$C$42,AH$42),2))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI43" s="2">
         <f t="shared" si="6"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AJ43" s="2">
         <f t="shared" si="6"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AK43" s="2">
         <f t="shared" si="6"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL43" s="2">
         <f t="shared" si="6"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM43" s="2">
         <f t="shared" si="6"/>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP43" s="38"/>
       <c r="AQ43" s="38"/>
       <c r="AR43" s="38"/>
     </row>
-    <row r="44" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="D44" s="2">
-        <v>2016</v>
+        <v>2027</v>
       </c>
       <c r="AP44" s="38"/>
       <c r="AQ44" s="38"/>
       <c r="AR44" s="38"/>
     </row>
-    <row r="45" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D45" s="2">
-        <v>2017</v>
+        <v>2028</v>
       </c>
       <c r="AP45" s="38"/>
       <c r="AQ45" s="38"/>
       <c r="AR45" s="38"/>
     </row>
-    <row r="46" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="2" t="s">
         <v>27</v>
       </c>
       <c r="D46" s="2">
-        <v>2018</v>
+        <v>2029</v>
       </c>
       <c r="AP46" s="38"/>
       <c r="AQ46" s="38"/>
       <c r="AR46" s="38"/>
     </row>
-    <row r="47" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="2" t="s">
         <v>28</v>
       </c>
       <c r="D47" s="2">
-        <v>2019</v>
+        <v>2030</v>
       </c>
       <c r="AP47" s="38"/>
       <c r="AQ47" s="38"/>
       <c r="AR47" s="38"/>
     </row>
-    <row r="48" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="2" t="s">
         <v>29</v>
       </c>
       <c r="D48" s="2">
-        <v>2020</v>
+        <v>2031</v>
       </c>
       <c r="AP48" s="38"/>
       <c r="AQ48" s="38"/>
       <c r="AR48" s="38"/>
     </row>
-    <row r="49" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D49" s="2">
-        <v>2021</v>
+        <v>2032</v>
       </c>
       <c r="AP49" s="38"/>
       <c r="AQ49" s="38"/>
       <c r="AR49" s="38"/>
     </row>
-    <row r="50" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="2" t="s">
         <v>31</v>
       </c>
       <c r="D50" s="2">
-        <v>2022</v>
+        <v>2033</v>
       </c>
       <c r="AP50" s="38"/>
       <c r="AQ50" s="38"/>
       <c r="AR50" s="38"/>
     </row>
-    <row r="51" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="2" t="s">
         <v>32</v>
       </c>
       <c r="D51" s="2">
-        <v>2023</v>
+        <v>2034</v>
       </c>
       <c r="AP51" s="38"/>
       <c r="AQ51" s="38"/>
       <c r="AR51" s="38"/>
     </row>
-    <row r="52" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D52" s="2">
-        <v>2024</v>
+        <v>2035</v>
       </c>
       <c r="AP52" s="38"/>
       <c r="AQ52" s="38"/>
       <c r="AR52" s="38"/>
     </row>
-    <row r="53" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="2" t="s">
         <v>34</v>
       </c>
       <c r="D53" s="2">
-        <v>2025</v>
+        <v>2036</v>
       </c>
       <c r="AP53" s="38"/>
       <c r="AQ53" s="38"/>
       <c r="AR53" s="38"/>
     </row>
-    <row r="54" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D54" s="2">
+        <v>2037</v>
+      </c>
       <c r="AP54" s="38"/>
       <c r="AQ54" s="38"/>
       <c r="AR54" s="38"/>
     </row>
-    <row r="55" spans="1:44" s="2" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="59" t="s">
-        <v>35</v>
-      </c>
-      <c r="B55" s="59" t="s">
-        <v>36</v>
-      </c>
-      <c r="C55" s="59"/>
-      <c r="D55" s="59"/>
+    <row r="55" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D55" s="2">
+        <v>2038</v>
+      </c>
       <c r="AP55" s="38"/>
       <c r="AQ55" s="38"/>
       <c r="AR55" s="38"/>
     </row>
-    <row r="56" spans="1:44" s="2" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="60" t="s">
-        <v>37</v>
-      </c>
-      <c r="B56" s="61" t="s">
-        <v>38</v>
-      </c>
-      <c r="C56" s="62" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56" s="62" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
+    <row r="56" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="2">
+        <v>2039</v>
       </c>
       <c r="AP56" s="38"/>
       <c r="AQ56" s="38"/>
       <c r="AR56" s="38"/>
     </row>
-    <row r="57" spans="1:44" s="2" customFormat="1" ht="16" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="60" t="s">
-        <v>13</v>
-      </c>
-      <c r="B57" s="61" t="s">
-        <v>40</v>
-      </c>
-      <c r="C57" s="62" t="s">
-        <v>41</v>
-      </c>
-      <c r="D57" s="62" t="b">
+    <row r="57" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="2">
+        <v>2040</v>
+      </c>
+      <c r="AP57" s="38"/>
+      <c r="AQ57" s="38"/>
+      <c r="AR57" s="38"/>
+    </row>
+    <row r="58" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AP58" s="38"/>
+      <c r="AQ58" s="38"/>
+      <c r="AR58" s="38"/>
+    </row>
+    <row r="59" spans="1:44" s="2" customFormat="1" ht="15" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="AP59" s="38"/>
+      <c r="AQ59" s="38"/>
+      <c r="AR59" s="38"/>
+    </row>
+    <row r="60" spans="1:44" s="2" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="C60" s="59"/>
+      <c r="D60" s="59"/>
+      <c r="AP60" s="38"/>
+      <c r="AQ60" s="38"/>
+      <c r="AR60" s="38"/>
+    </row>
+    <row r="61" spans="1:44" s="2" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="60" t="s">
+        <v>37</v>
+      </c>
+      <c r="B61" s="61" t="s">
+        <v>38</v>
+      </c>
+      <c r="C61" s="62" t="s">
+        <v>39</v>
+      </c>
+      <c r="D61" s="62" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:44" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15"/>
-    <row r="59" spans="1:44" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15"/>
-    <row r="60" spans="1:44" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15"/>
-    <row r="61" spans="1:44" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15"/>
-    <row r="62" spans="1:44" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15"/>
-    <row r="63" spans="1:44" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15"/>
-    <row r="64" spans="1:44" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15"/>
-    <row r="65" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15"/>
-    <row r="66" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
-      <c r="B66" s="2" t="s">
+      <c r="AP61" s="38"/>
+      <c r="AQ61" s="38"/>
+      <c r="AR61" s="38"/>
+    </row>
+    <row r="62" spans="1:44" s="2" customFormat="1" ht="17.25" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="B62" s="61" t="s">
+        <v>40</v>
+      </c>
+      <c r="C62" s="62" t="s">
+        <v>41</v>
+      </c>
+      <c r="D62" s="62" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:44" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:44" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="65" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="66" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="67" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="70" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="71" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C71" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D66" s="2">
+      <c r="D71" s="2">
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15">
-      <c r="B67" s="2" t="s">
+    <row r="72" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C72" s="1">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.15"/>
-    <row r="69" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="70" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="71" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="72" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="73" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="74" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="75" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
-    <row r="76" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="73" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="2:4" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="79" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="2:4" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
+    <row r="81" s="2" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="G3:AM3"/>
@@ -5565,12 +5620,11 @@
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" error="The Format should be P9999 for a project or a management code in 3 letters" prompt="_x000a_" sqref="A9:A23" xr:uid="{00000000-0002-0000-0000-000000000000}">
-      <formula1>IF(LEFT(A9,1)="P",OR(IF(LEN(A9)=5,IF(VALUE(RIGHT(A9,4))&lt;10000,1,0),0),IF(LEN(A9)=6,IF(VALUE(RIGHT(A9,5))&lt;100000,1,0),0)),VLOOKUP(A9,$A$55:$D$57,4,0))</formula1>
+      <formula1>IF(LEFT(A9,1)="P",OR(IF(LEN(A9)=5,IF(VALUE(RIGHT(A9,4))&lt;10000,1,0),0),IF(LEN(A9)=6,IF(VALUE(RIGHT(A9,5))&lt;100000,1,0),0)),VLOOKUP(A9,$A$60:$D$62,4,0))</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ4:AL4" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>YEARS</formula1>
-      <formula2>0</formula2>
+      <formula1>$D$42:$D$57</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD4" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>MONTHS</formula1>
